--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-deviceusestatement.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-deviceusestatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T12:03:31+00:00</t>
+    <t>2026-02-04T14:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -579,7 +579,7 @@
     <t>DeviceUseStatement.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest|4.0.1|Procedure|4.0.1|Claim|4.0.1|Observation|4.0.1|QuestionnaireResponse|4.0.1|DocumentReference|4.0.1)
+    <t xml:space="preserve">Reference(ServiceRequest|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-procedure|Claim|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation|QuestionnaireResponse|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-documentreference)
 </t>
   </si>
   <si>
@@ -636,7 +636,7 @@
     <t>DeviceUseStatement.source</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|RelatedPerson)
 </t>
   </si>
   <si>
@@ -693,7 +693,7 @@
     <t>DeviceUseStatement.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1|Media|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-condition|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-diagnosticreport|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-documentreference|Media)
 </t>
   </si>
   <si>
@@ -1075,7 +1075,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="109.078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="238.63671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-deviceusestatement.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-deviceusestatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T14:21:15+00:00</t>
+    <t>2026-02-04T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-deviceusestatement.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-deviceusestatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T15:46:20+00:00</t>
+    <t>2026-02-05T06:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-deviceusestatement.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-deviceusestatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T06:51:53+00:00</t>
+    <t>2026-02-05T08:33:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-deviceusestatement.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-deviceusestatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T08:33:30+00:00</t>
+    <t>2026-02-05T09:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-deviceusestatement.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-deviceusestatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T09:19:21+00:00</t>
+    <t>2026-02-05T09:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
